--- a/docs/submission/GlucoTwin_Research_Workbook.xlsx
+++ b/docs/submission/GlucoTwin_Research_Workbook.xlsx
@@ -15283,7 +15283,7 @@
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:11 UTC from repository HEAD 8c75de7 (working tree may differ)</t>
+          <t>2026-10-24 08:26 UTC from repository HEAD 07a7eac (working tree may differ)</t>
         </is>
       </c>
     </row>
